--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N57_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.51300754015332</v>
+        <v>7.720863725274915</v>
       </c>
       <c r="D2" t="n">
-        <v>47.3736136458304</v>
+        <v>7.69821221744744</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
